--- a/data_extactor/batch_10_fa/batch_0102_fa.xlsx
+++ b/data_extactor/batch_10_fa/batch_0102_fa.xlsx
@@ -508,27 +508,27 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>پایش | گوش دادن فعال | تفکر انتقادی | سخن گفتن | درک مطلب | یادگیری فعال</t>
+          <t>نظارت | گوش دادن فعال | تفکر انتقادی | سخن گفتن | درک مطلب | یادگیری فعال</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>مکانیک | امنیت و ایمنی عمومی | حمل‌ونقل | جغرافیا | مخابرات | زبان انگلیسی | مهندسی و فناوری</t>
+          <t>مکانیک | ایمنی و امنیت عمومی | حمل و نقل | جغرافیا | مخابرات | زبان انگلیسی | مهندسی و فناوری</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | تشخیص گفتار | وضوح گفتار | بینایی دور | بینایی نزدیک | توجه انتخابی | زمان عکس‌العمل | ترتیب‌دهی اطلاعات | استدلال استقرایی | توجه شنیداری | هماهنگی چند عضو | جهت‌یابی فضایی | استقامت | قدرت ایستا | هماهنگی کلی بدن | درک عمق | اشتراک زمانی | چالاکی دست | ثبات دست و بازو | دقت کنترل | کنترل سرعت</t>
+          <t>درک شفاهی | بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | تشخیص گفتار | وضوح گفتار | بینایی دور | بینایی نزدیک | توجه انتخابی | زمان عکس‌العمل | ترتیب‌دهی اطلاعات | استدلال استقرایی | توجه شنیداری | هماهنگی چند عضو | جهت‌گیری فضایی | استقامت | قدرت ایستا | هماهنگی کلی بدن | درک عمق | تقسیم توجه | مهارت دستی | ثبات دست و بازو | دقت کنترل | کنترل نرخ</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>بحث‌های چهره‌به‌چهره با افراد و در تیم‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | ارتباط با دیگران | پیامد خطا | اهمیت دقیق یا درست بودن | سلامت و ایمنی سایر کارکنان | فراوانی تصمیم‌گیری | فشار زمانی | نزدیکی فیزیکی | پوشیدن تجهیزات محافظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | قرار گرفتن در معرض شرایط خطرناک | قرار گرفتن در معرض تجهیزات خطرناک | فضای باز، در معرض تمام شرایط آب‌وهوایی | قرار گرفتن در معرض دمای بسیار گرم یا سرد | قرار گرفتن در معرض صداها و سطوح نویز مزاحم یا آزاردهنده | در یک خودروی سرپوشیده یا کار با تجهیزات سرپوشیده | قرار گرفتن در معرض فضای کاری تنگ، موقعیت‌های بدنی نامناسب | قرار گرفتن در معرض لرزش کل بدن | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها</t>
+          <t>گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | ارتباط با دیگران | پیامد خطا | اهمیت دقیق یا درست بودن | سلامت و ایمنی سایر کارکنان | فراوانی تصمیم‌گیری | فشار زمانی | نزدیکی فیزیکی | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | قرار گرفتن در معرض شرایط خطرناک | قرار گرفتن در معرض تجهیزات خطرناک | فضای باز، در معرض تمام شرایط آب و هوایی | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | در یک وسیله نقلیه محصور یا کار با تجهیزات محصور | قرار گرفتن در معرض فضای کاری تنگ، موقعیت‌های بدنی نامناسب | قرار گرفتن در معرض ارتعاش کل بدن | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>افسران گشت پلیس و کلانتر | سرپرستان رده‌اول پلیس و کارآگاهان | کارآگاهان و بازرسان جنایی | آتش‌نشانان | سرپرستان رده‌اول آتش‌نشانی و پیشگیری | نگهبانان امنیتی | افسران اصلاح و تربیت و زندانبانان | مدیران مدیریت بحران | غربالگرهای امنیت حمل‌ونقل | تکنسین‌های فوریت‌های پزشکی | مدیران کل و عملیاتی | متخصصان لجستیک | مدیران حمل‌ونقل، انبارداری و توزیع | مدیران ارشد اجرایی | متخصصان آموزش و توسعه | متخصصان بهداشت و ایمنی شغلی | افسران انطباق | تکنسین‌های نقشه‌برداری و نقشه‌کشی | کارگران مواد منفجره، متخصصان جابجایی مهمات و انفجارکاران | کارگران حذف مواد خطرناک</t>
+          <t>ماموران گشت پلیس و کلانتر | سرپرستان خط اول پلیس و کارآگاهان | کارآگاهان و بازرسان جنایی | آتش‌نشانان | سرپرستان خط اول آتش‌نشانی و پیشگیری | نگهبانان امنیتی | افسران اصلاح و تربیت و زندانبانان | مدیران مدیریت بحران | غربالگران امنیتی حمل و نقل | تکنسین‌های فوریت‌های پزشکی | مدیران عمومی و عملیات | لجستیسین‌ها | مدیران حمل‌ونقل، انبارداری و توزیع | مدیران ارشد اجرایی | متخصصان آموزش و توسعه | متخصصان بهداشت و ایمنی شغلی | افسران انطباق | تکنسین‌های نقشه‌برداری و نقشه‌کشی | کارگران مواد منفجره، متخصصان جابجایی مهمات و آتشبارها | کارگران حذف مواد خطرناک</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -565,27 +565,27 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>پایش | گوش دادن فعال | تفکر انتقادی | سخن گفتن | درک مطلب | یادگیری فعال | ریاضیات</t>
+          <t>نظارت | گوش دادن فعال | تفکر انتقادی | سخن گفتن | درک مطلب | یادگیری فعال | ریاضیات</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>ریاضیات | مکانیک | امنیت و ایمنی عمومی | فیزیک | جغرافیا | مهندسی و فناوری | زبان انگلیسی | کامپیوتر و الکترونیک</t>
+          <t>ریاضیات | مکانیک | ایمنی و امنیت عمومی | فیزیک | جغرافیا | مهندسی و فناوری | زبان انگلیسی | رایانه و الکترونیک</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | تشخیص گفتار | وضوح گفتار | بینایی دور | بینایی نزدیک | توجه انتخابی | زمان عکس‌العمل | ترتیب‌دهی اطلاعات | استدلال استقرایی | توجه شنیداری | هماهنگی چند عضو | جهت‌یابی فضایی | استقامت | قدرت ایستا | هماهنگی کلی بدن | درک عمق | اشتراک زمانی | استدلال ریاضی | سهولت در کار با اعداد | چالاکی دست | ثبات دست و بازو</t>
+          <t>درک شفاهی | بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | تشخیص گفتار | وضوح گفتار | بینایی دور | بینایی نزدیک | توجه انتخابی | زمان عکس‌العمل | ترتیب‌دهی اطلاعات | استدلال استقرایی | توجه شنیداری | هماهنگی چند عضو | جهت‌گیری فضایی | استقامت | قدرت ایستا | هماهنگی کلی بدن | درک عمق | تقسیم توجه | استدلال ریاضی | توانایی عددی | مهارت دستی | ثبات دست و بازو</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>بحث‌های چهره‌به‌چهره با افراد و در تیم‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | ارتباط با دیگران | پیامد خطا | اهمیت دقیق یا درست بودن | سلامت و ایمنی سایر کارکنان | فراوانی تصمیم‌گیری | فشار زمانی | نزدیکی فیزیکی | پوشیدن تجهیزات محافظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | قرار گرفتن در معرض شرایط خطرناک | قرار گرفتن در معرض تجهیزات خطرناک | فضای باز، در معرض تمام شرایط آب‌وهوایی | قرار گرفتن در معرض دمای بسیار گرم یا سرد | قرار گرفتن در معرض صداها و سطوح نویز مزاحم یا آزاردهنده | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | صرف زمان برای ایستادن | فضای باز، زیر سرپناه</t>
+          <t>گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | ارتباط با دیگران | پیامد خطا | اهمیت دقیق یا درست بودن | سلامت و ایمنی سایر کارکنان | فراوانی تصمیم‌گیری | فشار زمانی | نزدیکی فیزیکی | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | قرار گرفتن در معرض شرایط خطرناک | قرار گرفتن در معرض تجهیزات خطرناک | فضای باز، در معرض تمام شرایط آب و هوایی | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | صرف زمان برای ایستادن | فضای باز، زیر سقف</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>افسران گشت پلیس و کلانتر | سرپرستان رده‌اول پلیس و کارآگاهان | کارآگاهان و بازرسان جنایی | آتش‌نشانان | سرپرستان رده‌اول آتش‌نشانی و پیشگیری | نگهبانان امنیتی | افسران اصلاح و تربیت و زندانبانان | مدیران مدیریت بحران | غربالگرهای امنیت حمل‌ونقل | تکنسین‌های فوریت‌های پزشکی | مدیران کل و عملیاتی | متخصصان لجستیک | مدیران حمل‌ونقل، انبارداری و توزیع | مدیران ارشد اجرایی | متخصصان آموزش و توسعه | متخصصان بهداشت و ایمنی شغلی | افسران انطباق | تکنسین‌های نقشه‌برداری و نقشه‌کشی | کارگران مواد منفجره, متخصصان جابجایی مهمات و انفجارکاران | کارگران حذف مواد خطرناک</t>
+          <t>ماموران گشت پلیس و کلانتر | سرپرستان خط اول پلیس و کارآگاهان | کارآگاهان و بازرسان جنایی | آتش‌نشانان | سرپرستان خط اول آتش‌نشانی و پیشگیری | نگهبانان امنیتی | افسران اصلاح و تربیت و زندانبانان | مدیران مدیریت بحران | غربالگران امنیتی حمل و نقل | تکنسین‌های فوریت‌های پزشکی | مدیران عمومی و عملیات | لجستیسین‌ها | مدیران حمل‌ونقل، انبارداری و توزیع | مدیران ارشد اجرایی | متخصصان آموزش و توسعه | متخصصان بهداشت و ایمنی شغلی | افسران انطباق | تکنسین‌های نقشه‌برداری و نقشه‌کشی | کارگران مواد منفجره، متخصصان جابجایی مهمات و آتشبارها | کارگران حذف مواد خطرناک</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -622,27 +622,27 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>پایش | گوش دادن فعال | تفکر انتقادی | سخن گفتن | درک مطلب | یادگیری فعال</t>
+          <t>نظارت | گوش دادن فعال | تفکر انتقادی | سخن گفتن | درک مطلب | یادگیری فعال</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>مخابرات | کامپیوتر و الکترونیک | امنیت و ایمنی عمومی | جغرافیا | زبان انگلیسی | حمل‌ونقل | ارتباطات و رسانه | مهندسی و فناوری</t>
+          <t>مخابرات | رایانه و الکترونیک | ایمنی و امنیت عمومی | جغرافیا | زبان انگلیسی | حمل و نقل | ارتباطات و رسانه | مهندسی و فناوری</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | تشخیص گفتار | وضوح گفتار | بینایی دور | بینایی نزدیک | توجه انتخابی | زمان عکس‌العمل | ترتیب‌دهی اطلاعات | استدلال استقرایی | توجه شنیداری | هماهنگی چند عضو | جهت‌یابی فضایی | استقامت | قدرت ایستا | هماهنگی کلی بدن | درک عمق | اشتراک زمانی | سرعت ادراکی | انعطاف‌پذیری بستار | سرعت بستار | درک کتبی</t>
+          <t>درک شفاهی | بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | تشخیص گفتار | وضوح گفتار | بینایی دور | بینایی نزدیک | توجه انتخابی | زمان عکس‌العمل | ترتیب‌دهی اطلاعات | استدلال استقرایی | توجه شنیداری | هماهنگی چند عضو | جهت‌گیری فضایی | استقامت | قدرت ایستا | هماهنگی کلی بدن | درک عمق | تقسیم توجه | سرعت ادراکی | انعطاف‌پذیری بستار | سرعت بستار | درک کتبی</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>بحث‌های چهره‌به‌چهره با افراد و در تیم‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | ارتباط با دیگران | پیامد خطا | اهمیت دقیق یا درست بودن | سلامت و ایمنی سایر کارکنان | فراوانی تصمیم‌گیری | فشار زمانی | نزدیکی فیزیکی | پوشیدن تجهیزات محافظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | فضای بسته، با دمای کنترل‌شده | صرف زمان برای نشستن | اهمیت تکرار کارهای مشابه | درجه خودکارسازی | ایمیل | مکالمات تلفنی | نامه‌ها و یادداشت‌های مکتوب | قرار گرفتن در معرض صداها و سطوح نویز مزاحم یا آزاردهنده</t>
+          <t>گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | ارتباط با دیگران | پیامد خطا | اهمیت دقیق یا درست بودن | سلامت و ایمنی سایر کارکنان | فراوانی تصمیم‌گیری | فشار زمانی | نزدیکی فیزیکی | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | محیط داخلی، دارای کنترل شرایط محیطی | صرف زمان برای نشستن | اهمیت تکرار وظایف یکسان | میزان خودکارسازی | ایمیل | مکالمات تلفنی | نامه‌ها و یادداشت‌های کتبی | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>خلبانان، کمک‌خلبانان و مهندسان پرواز خطوط هوایی | خلبانان تجاری | کنترلرهای ترافیک هوایی | متخصصان عملیات فرودگاه | مکانیک‌ها و تکنسین‌های خدمات هواگرد | تکنسین‌های اویونیک | مهندسان هوافضا | تکنسین‌ها و فناوران مهندسی و عملیات هوافضا | مدیران مدیریت بحران | مدیران حمل‌ونقل، انبارداری و توزیع | متخصصان لجستیک | مدیران کل و عملیاتی | مدیران ارشد اجرایی | سرپرستان رده‌اول پلیس و کارآگاهان | کارآگاهان و بازرسان جنایی | افسران گشت پلیس و کلانتر | نگهبانان امنیتی | غربالگرهای امنیت حمل‌ونقل | متخصصان آموزش و توسعه | متخصصان بهداشت و ایمنی شغلی</t>
+          <t>خلبانان، کمک‌خلبانان و مهندسان پرواز خطوط هوایی | خلبانان تجاری | کنترلرهای ترافیک هوایی | متخصصان عملیات فرودگاه | مکانیک‌ها و تکنسین‌های خدمات هواپیما | تکنسین‌های هوانوردی | مهندسان هوافضا | تکنسین‌ها و کارشناسان مهندسی و عملیات هوافضا | مدیران مدیریت بحران | مدیران حمل‌ونقل، انبارداری و توزیع | لجستیسین‌ها | مدیران عمومی و عملیات | مدیران ارشد اجرایی | سرپرستان خط اول پلیس و کارآگاهان | کارآگاهان و بازرسان جنایی | ماموران گشت پلیس و کلانتر | نگهبانان امنیتی | غربالگران امنیتی حمل و نقل | متخصصان آموزش و توسعه | متخصصان بهداشت و ایمنی شغلی</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -679,27 +679,27 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>پایش | گوش دادن فعال | تفکر انتقادی | سخن گفتن | درک مطلب | یادگیری فعال</t>
+          <t>نظارت | گوش دادن فعال | تفکر انتقادی | سخن گفتن | درک مطلب | یادگیری فعال</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>امنیت و ایمنی عمومی | جغرافیا | مکانیک | مخابرات | زبان انگلیسی | حمل‌ونقل | آموزش و پرورش</t>
+          <t>ایمنی و امنیت عمومی | جغرافیا | مکانیک | مخابرات | زبان انگلیسی | حمل و نقل | آموزش و پرورش</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | تشخیص گفتار | وضوح گفتار | بینایی دور | بینایی نزدیک | توجه انتخابی | زمان عکس‌العمل | ترتیب‌دهی اطلاعات | استدلال استقرایی | توجه شنیداری | هماهنگی چند عضو | جهت‌یابی فضایی | استقامت | قدرت ایستا | هماهنگی کلی بدن | درک عمق | اشتراک زمانی | قدرت تنه | قدرت پویا | انعطاف‌پذیری حرکتی | دید در شب</t>
+          <t>درک شفاهی | بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | تشخیص گفتار | وضوح گفتار | بینایی دور | بینایی نزدیک | توجه انتخابی | زمان عکس‌العمل | ترتیب‌دهی اطلاعات | استدلال استقرایی | توجه شنیداری | هماهنگی چند عضو | جهت‌گیری فضایی | استقامت | قدرت ایستا | هماهنگی کلی بدن | درک عمق | تقسیم توجه | قدرت تنه | قدرت پویا | انعطاف‌پذیری دامنه حرکت | بینایی در شب</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>بحث‌های چهره‌به‌چهره با افراد و در تیم‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | ارتباط با دیگران | پیامد خطا | اهمیت دقیق یا درست بودن | سلامت و ایمنی سایر کارکنان | فراوانی تصمیم‌گیری | فشار زمانی | نزدیکی فیزیکی | پوشیدن تجهیزات محافظتی یا ایمنی معمول مانند کفش ایمنی، عینک, دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | قرار گرفتن در معرض شرایط خطرناک | قرار گرفتن در معرض تجهیزات خطرناک | فضای باز، در معرض تمام شرایط آب‌وهوایی | قرار گرفتن در معرض دمای بسیار گرم یا سرد | قرار گرفتن در معرض صداها و سطوح نویز مزاحم یا آزاردهنده | برخورد با افراد خشن یا از نظر فیزیکی پرخاشگر | پوشیدن تجهیزات محافظتی یا ایمنی تخصصی مانند دستگاه تنفس، مهار ایمنی، لباس‌های محافظ کامل یا محافظت در برابر تشعشع | صرف زمان برای راه رفتن یا دویدن | صرف زمان برای ایستادن | صرف زمان برای زانو زدن، چمباتمه زدن، خم شدن یا خزیدن | صرف زمان برای خم کردن یا چرخاندن بدن</t>
+          <t>گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | ارتباط با دیگران | پیامد خطا | اهمیت دقیق یا درست بودن | سلامت و ایمنی سایر کارکنان | فراوانی تصمیم‌گیری | فشار زمانی | نزدیکی فیزیکی | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | قرار گرفتن در معرض شرایط خطرناک | قرار گرفتن در معرض تجهیزات خطرناک | فضای باز، در معرض تمام شرایط آب و هوایی | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | برخورد با افراد خشن یا از نظر فیزیکی پرخاشگر | استفاده از تجهیزات حفاظتی یا ایمنی تخصصی مانند دستگاه تنفس، هارنس ایمنی، لباس‌های محافظ کامل یا محافظت در برابر تشعشع | صرف زمان برای راه رفتن یا دویدن | صرف زمان برای ایستادن | صرف زمان برای زانو زدن، چمباتمه زدن، خم شدن یا خزیدن | صرف زمان برای خم کردن یا چرخاندن بدن</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>افسران گشت پلیس و کلانتر | سرپرستان رده‌اول پلیس و کارآگاهان | کارآگاهان و بازرسان جنایی | آتش‌نشانان | سرپرستان رده‌اول آتش‌نشانی و پیشگیری | نگهبانان امنیتی | افسران اصلاح و تربیت و زندانبانان | مدیران مدیریت بحران | غربالگرهای امنیت حمل‌ونقل | تکنسین‌های فوریت‌های پزشکی | مدیران کل و عملیاتی | متخصصان لجستیک | مدیران حمل‌ونقل، انبارداری و توزیع | مدیران ارشد اجرایی | متخصصان آموزش و توسعه | متخصصان بهداشت و ایمنی شغلی | افسران انطباق | تکنسین‌های نقشه‌برداری و نقشه‌کشی | کارگران مواد منفجره، متخصصان جابجایی مهمات و انفجارکاران | کارگران حذف مواد خطرناک</t>
+          <t>ماموران گشت پلیس و کلانتر | سرپرستان خط اول پلیس و کارآگاهان | کارآگاهان و بازرسان جنایی | آتش‌نشانان | سرپرستان خط اول آتش‌نشانی و پیشگیری | نگهبانان امنیتی | افسران اصلاح و تربیت و زندانبانان | مدیران مدیریت بحران | غربالگران امنیتی حمل و نقل | تکنسین‌های فوریت‌های پزشکی | مدیران عمومی و عملیات | لجستیسین‌ها | مدیران حمل‌ونقل، انبارداری و توزیع | مدیران ارشد اجرایی | متخصصان آموزش و توسعه | متخصصان بهداشت و ایمنی شغلی | افسران انطباق | تکنسین‌های نقشه‌برداری و نقشه‌کشی | کارگران مواد منفجره، متخصصان جابجایی مهمات و آتشبارها | کارگران حذف مواد خطرناک</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -736,27 +736,27 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>پایش | گوش دادن فعال | تفکر انتقادی | سخن گفتن | درک مطلب | یادگیری فعال | نگارش</t>
+          <t>نظارت | گوش دادن فعال | تفکر انتقادی | سخن گفتن | درک مطلب | یادگیری فعال | نگارش</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>امنیت و ایمنی عمومی | جغرافیا | زبان خارجی | مخابرات | پزشکی و دندانپزشکی | زبان انگلیسی | جامعه‌شناسی و انسان‌شناسی | آموزش و پرورش | مکانیک</t>
+          <t>ایمنی و امنیت عمومی | جغرافیا | زبان خارجی | مخابرات | پزشکی و دندان‌پزشکی | زبان انگلیسی | جامعه‌شناسی و انسان‌شناسی | آموزش و پرورش | مکانیک</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | تشخیص گفتار | وضوح گفتار | بینایی دور | بینایی نزدیک | توجه انتخابی | زمان عکس‌العمل | ترتیب‌دهی اطلاعات | استدلال استقرایی | توجه شنیداری | هماهنگی چند عضو | جهت‌یابی فضایی | استقامت | قدرت ایستا | هماهنگی کلی بدن | درک عمق | اشتراک زمانی | قدرت تنه | قدرت پویا | حفظ کردن | دید در شب | تعادل کلی بدن</t>
+          <t>درک شفاهی | بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | تشخیص گفتار | وضوح گفتار | بینایی دور | بینایی نزدیک | توجه انتخابی | زمان عکس‌العمل | ترتیب‌دهی اطلاعات | استدلال استقرایی | توجه شنیداری | هماهنگی چند عضو | جهت‌گیری فضایی | استقامت | قدرت ایستا | هماهنگی کلی بدن | درک عمق | تقسیم توجه | قدرت تنه | قدرت پویا | حفظ کردن | بینایی در شب | تعادل کلی بدن</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>بحث‌های چهره‌به‌چهره با افراد و در تیم‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | ارتباط با دیگران | پیامد خطا | اهمیت دقیق یا درست بودن | سلامت و ایمنی سایر کارکنان | فراوانی تصمیم‌گیری | فشار زمانی | نزدیکی فیزیکی | پوشیدن تجهیزات محافظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | قرار گرفتن در معرض شرایط خطرناک | قرار گرفتن در معرض تجهیزات خطرناک | فضای باز، در معرض تمام شرایط آب‌وهوایی | قرار گرفتن در معرض دمای بسیار گرم یا سرد | قرار گرفتن در معرض صداها و سطوح نویز مزاحم یا آزاردهنده | برخورد با افراد خشن یا از نظر فیزیکی پرخاشگر | پوشیدن تجهیزات محافظتی یا ایمنی تخصصی مانند دستگاه تنفس، مهار ایمنی، لباس‌های محافظ کامل یا محافظت در برابر تشعشع | صرف زمان برای راه رفتن یا دویدن | قرار گرفتن در معرض ارتفاعات بالا | صرف زمان برای زانو زدن، چمباتمه زدن، خم شدن یا خزیدن | صرف زمان برای حفظ یا بازیابی تعادل</t>
+          <t>گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | ارتباط با دیگران | پیامد خطا | اهمیت دقیق یا درست بودن | سلامت و ایمنی سایر کارکنان | فراوانی تصمیم‌گیری | فشار زمانی | نزدیکی فیزیکی | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | قرار گرفتن در معرض شرایط خطرناک | قرار گرفتن در معرض تجهیزات خطرناک | فضای باز، در معرض تمام شرایط آب و هوایی | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | برخورد با افراد خشن یا از نظر فیزیکی پرخاشگر | استفاده از تجهیزات حفاظتی یا ایمنی تخصصی مانند دستگاه تنفس، هارنس ایمنی، لباس‌های محافظ کامل یا محافظت در برابر تشعشع | صرف زمان برای راه رفتن یا دویدن | قرار گرفتن در معرض ارتفاعات بالا | صرف زمان برای زانو زدن، چمباتمه زدن، خم شدن یا خزیدن | صرف زمان برای حفظ یا بازیابی تعادل</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>افسران گشت پلیس و کلانتر | سرپرستان رده‌اول پلیس و کارآگاهان | کارآگاهان و بازرسان جنایی | آتش‌نشانان | سرپرستان رده‌اول آتش‌نشانی و پیشگیری | نگهبانان امنیتی | افسران اصلاح و تربیت و زندانبانان | مدیران مدیریت بحران | غربالگرهای امنیت حمل‌ونقل | تکنسین‌های فوریت‌های پزشکی | مدیران کل و عملیاتی | متخصصان لجستیک | مدیران حمل‌ونقل، انبارداری و توزیع | مدیران ارشد اجرایی | متخصصان آموزش و توسعه | متخصصان بهداشت و ایمنی شغلی | افسران انطباق | تکنسین‌های نقشه‌برداری و نقشه‌کشی | کارگران مواد منفجره، متخصصان جابجایی مهمات و انفجارکاران | کارگران حذف مواد خطرناک</t>
+          <t>ماموران گشت پلیس و کلانتر | سرپرستان خط اول پلیس و کارآگاهان | کارآگاهان و بازرسان جنایی | آتش‌نشانان | سرپرستان خط اول آتش‌نشانی و پیشگیری | نگهبانان امنیتی | افسران اصلاح و تربیت و زندانبانان | مدیران مدیریت بحران | غربالگران امنیتی حمل و نقل | تکنسین‌های فوریت‌های پزشکی | مدیران عمومی و عملیات | لجستیسین‌ها | مدیران حمل‌ونقل، انبارداری و توزیع | مدیران ارشد اجرایی | متخصصان آموزش و توسعه | متخصصان بهداشت و ایمنی شغلی | افسران انطباق | تکنسین‌های نقشه‌برداری و نقشه‌کشی | کارگران مواد منفجره، متخصصان جابجایی مهمات و آتشبارها | کارگران حذف مواد خطرناک</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -793,27 +793,27 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>پایش | گوش دادن فعال | تفکر انتقادی | سخن گفتن | درک مطلب | یادگیری فعال</t>
+          <t>نظارت | گوش دادن فعال | تفکر انتقادی | سخن گفتن | درک مطلب | یادگیری فعال</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>امنیت و ایمنی عمومی | مکانیک | مخابرات | جغرافیا | زبان انگلیسی | کامپیوتر و الکترونیک | حمل‌ونقل</t>
+          <t>ایمنی و امنیت عمومی | مکانیک | مخابرات | جغرافیا | زبان انگلیسی | رایانه و الکترونیک | حمل و نقل</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | تشخیص گفتار | وضوح گفتار | بینایی دور | بینایی نزدیک | توجه انتخابی | زمان عکس‌العمل | ترتیب‌دهی اطلاعات | استدلال استقرایی | توجه شنیداری | هماهنگی چند عضو | جهت‌یابی فضایی | استقامت | قدرت ایستا | هماهنگی کلی بدن | درک عمق | اشتراک زمانی</t>
+          <t>درک شفاهی | بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | تشخیص گفتار | وضوح گفتار | بینایی دور | بینایی نزدیک | توجه انتخابی | زمان عکس‌العمل | ترتیب‌دهی اطلاعات | استدلال استقرایی | توجه شنیداری | هماهنگی چند عضو | جهت‌گیری فضایی | استقامت | قدرت ایستا | هماهنگی کلی بدن | درک عمق | تقسیم توجه</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>بحث‌های چهره‌به‌چهره با افراد و در تیم‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | ارتباط با دیگران | پیامد خطا | اهمیت دقیق یا درست بودن | سلامت و ایمنی سایر کارکنان | فراوانی تصمیم‌گیری | فشار زمانی | نزدیکی فیزیکی | پوشیدن تجهیزات محافظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | قرار گرفتن در معرض شرایط خطرناک | قرار گرفتن در معرض تجهیزات خطرناک | فضای باز، در معرض تمام شرایط آب‌وهوایی | قرار گرفتن در معرض دمای بسیار گرم یا سرد | قرار گرفتن در معرض صداها و سطوح نویز مزاحم یا آزاردهنده | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها</t>
+          <t>گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | ارتباط با دیگران | پیامد خطا | اهمیت دقیق یا درست بودن | سلامت و ایمنی سایر کارکنان | فراوانی تصمیم‌گیری | فشار زمانی | نزدیکی فیزیکی | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | قرار گرفتن در معرض شرایط خطرناک | قرار گرفتن در معرض تجهیزات خطرناک | فضای باز، در معرض تمام شرایط آب و هوایی | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>افسران گشت پلیس و کلانتر | سرپرستان رده‌اول پلیس و کارآگاهان | کارآگاهان و بازرسان جنایی | آتش‌نشانان | سرپرستان رده‌اول آتش‌نشانی و پیشگیری | نگهبانان امنیتی | افسران اصلاح و تربیت و زندانبانان | مدیران مدیریت بحران | غربالگرهای امنیت حمل‌ونقل | تکنسین‌های فوریت‌های پزشکی | مدیران کل و عملیاتی | متخصصان لجستیک | مدیران حمل‌ونقل، انبارداری و توزیع | مدیران ارشد اجرایی | متخصصان آموزش و توسعه | متخصصان بهداشت و ایمنی شغلی | افسران انطباق | تکنسین‌های نقشه‌برداری و نقشه‌کشی | کارگران مواد منفجره، متخصصان جابجایی مهمات و انفجارکاران | کارگران حذف مواد خطرناک</t>
+          <t>ماموران گشت پلیس و کلانتر | سرپرستان خط اول پلیس و کارآگاهان | کارآگاهان و بازرسان جنایی | آتش‌نشانان | سرپرستان خط اول آتش‌نشانی و پیشگیری | نگهبانان امنیتی | افسران اصلاح و تربیت و زندانبانان | مدیران مدیریت بحران | غربالگران امنیتی حمل و نقل | تکنسین‌های فوریت‌های پزشکی | مدیران عمومی و عملیات | لجستیسین‌ها | مدیران حمل‌ونقل، انبارداری و توزیع | مدیران ارشد اجرایی | متخصصان آموزش و توسعه | متخصصان بهداشت و ایمنی شغلی | افسران انطباق | تکنسین‌های نقشه‌برداری و نقشه‌کشی | کارگران مواد منفجره، متخصصان جابجایی مهمات و آتشبارها | کارگران حذف مواد خطرناک</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">

--- a/data_extactor/batch_10_fa/batch_0102_fa.xlsx
+++ b/data_extactor/batch_10_fa/batch_0102_fa.xlsx
@@ -508,17 +508,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>نظارت | شنیدن فعال | تفکر انتقادی | سخن گفتن | درک مطلب | یادگیری فعال</t>
+          <t>نظارت | گوش دادن فعال | تفکر انتقادی | سخن گفتن | درک مطلب | یادگیری فعال</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>مکانیک | ایمنی و امنیت عمومی | حمل‌ونقل | جغرافیا | مخابرات | زبان انگلیسی | مهندسی و فناوری</t>
+          <t>مکانیک | ایمنی و امنیت عمومی | حمل و نقل | جغرافیا | مخابرات | زبان انگلیسی | مهندسی و فناوری</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | تشخیص گفتار | وضوح گفتار | دید دور | دید نزدیک | توجه انتخابی | زمان واکنش | مرتب‌سازی اطلاعات | استدلال استقرایی | توجه شنیداری | هماهنگی چندعضوی | جهت‌یابی فضایی | استقامت | استحکام ایستا | هماهنگی کلی بدن | درک عمق | تقسیم توجه | چابکی دستی | ثبات دست و بازو | دقت کنترل | کنترل سرعت</t>
+          <t>درک شفاهی | بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | تشخیص گفتار | وضوح گفتار | بینایی دور | بینایی نزدیک | توجه انتخابی | زمان عکس‌العمل | ترتیب‌دهی اطلاعات | استدلال استقرایی | توجه شنیداری | هماهنگی چند عضو | جهت‌گیری فضایی | استقامت | قدرت ایستا | هماهنگی کلی بدن | درک عمق | تقسیم توجه | مهارت دستی | ثبات دست و بازو | دقت کنترل | کنترل نرخ</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -528,7 +528,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>افسران گشت پلیس و کلانتری | سرپرستان رده‌اول پلیس و کارآگاهان | کارآگاهان و بازرسان جنایی | آتش‌نشانان | سرپرستان رده‌اول آتش‌نشانی و پیشگیری از حریق | نگهبانان و ماموران حفاظتی | افسران و زندانبانان ندامتگاه‌ها | مدیران مدیریت بحران و فوریت‌ها | ماموران بازرسی امنیت حمل‌ونقل | تکنسین‌های فوریت‌های پزشکی | مدیران ارشد و عملیاتی | کارشناسان لجستیک و زنجیره تامین | مدیران حمل‌ونقل، انبارداری و توزیع | مدیران عامل و مدیران ارشد اجرایی | کارشناسان آموزش و توسعه منابع انسانی | کارشناسان بهداشت حرفه‌ای و ایمنی کار | کارشناسان نظارت و انطباق با مقررات | تکنسین‌های نقشه‌برداری | تکنسین‌های مواد ناریه، مهمات و انفجار | کارگران پاکسازی و دفع مواد خطرناک</t>
+          <t>ماموران گشت پلیس و کلانتری | سرپرستان رده‌اول پلیس و کارآگاهان | کارآگاهان و بازرسان جنایی | آتش‌نشانان | سرپرستان رده‌اول آتش‌نشانی و خدمات ایمنی و پیشگیری | نگهبانان و ماموران حراست | مأموران زندان و بازداشتگاه | مدیران مدیریت بحران و پدافند غیرعامل | ماموران بازرسی و کنترل امنیتی حمل‌ونقل | تکنسین‌های فوریت‌های پزشکی | مدیران کل و مدیران عملیات | کارشناسان لجستیک و مدیریت زنجیره تأمین | مدیران حمل‌ونقل، انبارداری و توزیع | مدیران عامل و مدیران ارشد اجرایی | کارشناسان آموزش و توسعه منابع انسانی | کارشناسان بهداشت حرفه‌ای و ایمنی کار | کارشناسان پایش انطباق و بازرسی مقرراتی | تکنسین‌های نقشه‌برداری و نقشه‌نگاری | کارشناسان مواد منفجره و آتش‌باری | کارگران امحا و پاک‌سازی مواد خطرناک</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -565,7 +565,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>نظارت | شنیدن فعال | تفکر انتقادی | سخن گفتن | درک مطلب | یادگیری فعال | ریاضیات</t>
+          <t>نظارت | گوش دادن فعال | تفکر انتقادی | سخن گفتن | درک مطلب | یادگیری فعال | ریاضیات</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -575,7 +575,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | تشخیص گفتار | وضوح گفتار | دید دور | دید نزدیک | توجه انتخابی | زمان واکنش | مرتب‌سازی اطلاعات | استدلال استقرایی | توجه شنیداری | هماهنگی چندعضوی | جهت‌یابی فضایی | استقامت | استحکام ایستا | هماهنگی کلی بدن | درک عمق | تقسیم توجه | استدلال ریاضی | محاسبات عددی | چابکی دستی | ثبات دست و بازو</t>
+          <t>درک شفاهی | بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | تشخیص گفتار | وضوح گفتار | بینایی دور | بینایی نزدیک | توجه انتخابی | زمان عکس‌العمل | ترتیب‌دهی اطلاعات | استدلال استقرایی | توجه شنیداری | هماهنگی چند عضو | جهت‌گیری فضایی | استقامت | قدرت ایستا | هماهنگی کلی بدن | درک عمق | تقسیم توجه | استدلال ریاضی | توانایی عددی | مهارت دستی | ثبات دست و بازو</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>افسران گشت پلیس و کلانتری | سرپرستان رده‌اول پلیس و کارآگاهان | کارآگاهان و بازرسان جنایی | آتش‌نشانان | سرپرستان رده‌اول آتش‌نشانی و پیشگیری از حریق | نگهبانان و ماموران حفاظتی | افسران و زندانبانان ندامتگاه‌ها | مدیران مدیریت بحران و فوریت‌ها | ماموران بازرسی امنیت حمل‌ونقل | تکنسین‌های فوریت‌های پزشکی | مدیران ارشد و عملیاتی | کارشناسان لجستیک و زنجیره تامین | مدیران حمل‌ونقل، انبارداری و توزیع | مدیران عامل و مدیران ارشد اجرایی | کارشناسان آموزش و توسعه منابع انسانی | کارشناسان بهداشت حرفه‌ای و ایمنی کار | کارشناسان نظارت و انطباق با مقررات | تکنسین‌های نقشه‌برداری | تکنسین‌های مواد ناریه، مهمات و انفجار | کارگران پاکسازی و دفع مواد خطرناک</t>
+          <t>ماموران گشت پلیس و کلانتری | سرپرستان رده‌اول پلیس و کارآگاهان | کارآگاهان و بازرسان جنایی | آتش‌نشانان | سرپرستان رده‌اول آتش‌نشانی و خدمات ایمنی و پیشگیری | نگهبانان و ماموران حراست | مأموران زندان و بازداشتگاه | مدیران مدیریت بحران و پدافند غیرعامل | ماموران بازرسی و کنترل امنیتی حمل‌ونقل | تکنسین‌های فوریت‌های پزشکی | مدیران کل و مدیران عملیات | کارشناسان لجستیک و مدیریت زنجیره تأمین | مدیران حمل‌ونقل، انبارداری و توزیع | مدیران عامل و مدیران ارشد اجرایی | کارشناسان آموزش و توسعه منابع انسانی | کارشناسان بهداشت حرفه‌ای و ایمنی کار | کارشناسان پایش انطباق و بازرسی مقرراتی | تکنسین‌های نقشه‌برداری و نقشه‌نگاری | کارشناسان مواد منفجره و آتش‌باری | کارگران امحا و پاک‌سازی مواد خطرناک</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -622,17 +622,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>نظارت | شنیدن فعال | تفکر انتقادی | سخن گفتن | درک مطلب | یادگیری فعال</t>
+          <t>نظارت | گوش دادن فعال | تفکر انتقادی | سخن گفتن | درک مطلب | یادگیری فعال</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>مخابرات | رایانه و الکترونیک | ایمنی و امنیت عمومی | جغرافیا | زبان انگلیسی | حمل‌ونقل | ارتباطات و رسانه | مهندسی و فناوری</t>
+          <t>مخابرات | رایانه و الکترونیک | ایمنی و امنیت عمومی | جغرافیا | زبان انگلیسی | حمل و نقل | ارتباطات و رسانه | مهندسی و فناوری</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | تشخیص گفتار | وضوح گفتار | دید دور | دید نزدیک | توجه انتخابی | زمان واکنش | مرتب‌سازی اطلاعات | استدلال استقرایی | توجه شنیداری | هماهنگی چندعضوی | جهت‌یابی فضایی | استقامت | استحکام ایستا | هماهنگی کلی بدن | درک عمق | تقسیم توجه | سرعت ادراک | انعطاف‌پذیری بستار | سرعت بستار | درک کتبی</t>
+          <t>درک شفاهی | بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | تشخیص گفتار | وضوح گفتار | بینایی دور | بینایی نزدیک | توجه انتخابی | زمان عکس‌العمل | ترتیب‌دهی اطلاعات | استدلال استقرایی | توجه شنیداری | هماهنگی چند عضو | جهت‌گیری فضایی | استقامت | قدرت ایستا | هماهنگی کلی بدن | درک عمق | تقسیم توجه | سرعت ادراکی | انعطاف‌پذیری بستار | سرعت بستار | درک کتبی</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>خلبانان، کمک‌خلبانان و مهندسان پرواز خطوط هوایی | خلبانان تجاری | کنترلرهای ترافیک هوایی | متخصصان عملیات فرودگاهی | مکانیک‌ها و تکنسین‌های تعمیر و نگهداری هواگرد | تکنسین‌های اویونیک و الکترونیک هوانوردی | مهندسان هوافضا | تکنسین‌های مهندسی هوافضا و عملیات پرواز | مدیران مدیریت بحران و فوریت‌ها | مدیران حمل‌ونقل، انبارداری و توزیع | کارشناسان لجستیک و زنجیره تامین | مدیران ارشد و عملیاتی | مدیران عامل و مدیران ارشد اجرایی | سرپرستان رده‌اول پلیس و کارآگاهان | کارآگاهان و بازرسان جنایی | افسران گشت پلیس و کلانتری | نگهبانان و ماموران حفاظتی | ماموران بازرسی امنیت حمل‌ونقل | کارشناسان آموزش و توسعه منابع انسانی | کارشناسان بهداشت حرفه‌ای و ایمنی کار</t>
+          <t>خلبانان خطوط هوایی، کمک‌خلبانان و مهندسان پرواز | خلبانان تجاری | کنترلرهای ترافیک هوایی | کارشناسان عملیات فرودگاهی | مکانیک و تکنسین خدمات هواپیما | تکنسین‌های اویونیک و الکترونیک پرواز | مهندسان هوافضا | کارشناسان و تکنسین‌های مهندسی و عملیات هوافضا | مدیران مدیریت بحران و پدافند غیرعامل | مدیران حمل‌ونقل، انبارداری و توزیع | کارشناسان لجستیک و مدیریت زنجیره تأمین | مدیران کل و مدیران عملیات | مدیران عامل و مدیران ارشد اجرایی | سرپرستان رده‌اول پلیس و کارآگاهان | کارآگاهان و بازرسان جنایی | ماموران گشت پلیس و کلانتری | نگهبانان و ماموران حراست | ماموران بازرسی و کنترل امنیتی حمل‌ونقل | کارشناسان آموزش و توسعه منابع انسانی | کارشناسان بهداشت حرفه‌ای و ایمنی کار</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -679,17 +679,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>نظارت | شنیدن فعال | تفکر انتقادی | سخن گفتن | درک مطلب | یادگیری فعال</t>
+          <t>نظارت | گوش دادن فعال | تفکر انتقادی | سخن گفتن | درک مطلب | یادگیری فعال</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>ایمنی و امنیت عمومی | جغرافیا | مکانیک | مخابرات | زبان انگلیسی | حمل‌ونقل | آموزش و تدریس</t>
+          <t>ایمنی و امنیت عمومی | جغرافیا | مکانیک | مخابرات | زبان انگلیسی | حمل و نقل | آموزش و پرورش</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | تشخیص گفتار | وضوح گفتار | دید دور | دید نزدیک | توجه انتخابی | زمان واکنش | مرتب‌سازی اطلاعات | استدلال استقرایی | توجه شنیداری | هماهنگی چندعضوی | جهت‌یابی فضایی | استقامت | استحکام ایستا | هماهنگی کلی بدن | درک عمق | تقسیم توجه | قدرت تنه | قدرت پویا | انعطاف‌پذیری دامنه‌ای | دید در شب</t>
+          <t>درک شفاهی | بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | تشخیص گفتار | وضوح گفتار | بینایی دور | بینایی نزدیک | توجه انتخابی | زمان عکس‌العمل | ترتیب‌دهی اطلاعات | استدلال استقرایی | توجه شنیداری | هماهنگی چند عضو | جهت‌گیری فضایی | استقامت | قدرت ایستا | هماهنگی کلی بدن | درک عمق | تقسیم توجه | قدرت تنه | قدرت پویا | انعطاف‌پذیری دامنه حرکت | بینایی در شب</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>افسران گشت پلیس و کلانتری | سرپرستان رده‌اول پلیس و کارآگاهان | کارآگاهان و بازرسان جنایی | آتش‌نشانان | سرپرستان رده‌اول آتش‌نشانی و پیشگیری از حریق | نگهبانان و ماموران حفاظتی | افسران و زندانبانان ندامتگاه‌ها | مدیران مدیریت بحران و فوریت‌ها | ماموران بازرسی امنیت حمل‌ونقل | تکنسین‌های فوریت‌های پزشکی | مدیران ارشد و عملیاتی | کارشناسان لجستیک و زنجیره تامین | مدیران حمل‌ونقل، انبارداری و توزیع | مدیران عامل و مدیران ارشد اجرایی | کارشناسان آموزش و توسعه منابع انسانی | کارشناسان بهداشت حرفه‌ای و ایمنی کار | کارشناسان نظارت و انطباق با مقررات | تکنسین‌های نقشه‌برداری | تکنسین‌های مواد ناریه، مهمات و انفجار | کارگران پاکسازی و دفع مواد خطرناک</t>
+          <t>ماموران گشت پلیس و کلانتری | سرپرستان رده‌اول پلیس و کارآگاهان | کارآگاهان و بازرسان جنایی | آتش‌نشانان | سرپرستان رده‌اول آتش‌نشانی و خدمات ایمنی و پیشگیری | نگهبانان و ماموران حراست | مأموران زندان و بازداشتگاه | مدیران مدیریت بحران و پدافند غیرعامل | ماموران بازرسی و کنترل امنیتی حمل‌ونقل | تکنسین‌های فوریت‌های پزشکی | مدیران کل و مدیران عملیات | کارشناسان لجستیک و مدیریت زنجیره تأمین | مدیران حمل‌ونقل، انبارداری و توزیع | مدیران عامل و مدیران ارشد اجرایی | کارشناسان آموزش و توسعه منابع انسانی | کارشناسان بهداشت حرفه‌ای و ایمنی کار | کارشناسان پایش انطباق و بازرسی مقرراتی | تکنسین‌های نقشه‌برداری و نقشه‌نگاری | کارشناسان مواد منفجره و آتش‌باری | کارگران امحا و پاک‌سازی مواد خطرناک</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -736,17 +736,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>نظارت | شنیدن فعال | تفکر انتقادی | سخن گفتن | درک مطلب | یادگیری فعال | نگارش</t>
+          <t>نظارت | گوش دادن فعال | تفکر انتقادی | سخن گفتن | درک مطلب | یادگیری فعال | نگارش</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>ایمنی و امنیت عمومی | جغرافیا | زبان‌های خارجی | مخابرات | پزشکی و دندانپزشکی | زبان انگلیسی | جامعه‌شناسی و مردم‌شناسی | آموزش و تدریس | مکانیک</t>
+          <t>ایمنی و امنیت عمومی | جغرافیا | زبان خارجی | مخابرات | پزشکی و دندان‌پزشکی | زبان انگلیسی | جامعه‌شناسی و انسان‌شناسی | آموزش و پرورش | مکانیک</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | تشخیص گفتار | وضوح گفتار | دید دور | دید نزدیک | توجه انتخابی | زمان واکنش | مرتب‌سازی اطلاعات | استدلال استقرایی | توجه شنیداری | هماهنگی چندعضوی | جهت‌یابی فضایی | استقامت | استحکام ایستا | هماهنگی کلی بدن | درک عمق | تقسیم توجه | قدرت تنه | قدرت پویا | به‌خاطرسپاری | دید در شب | تعادل کلی بدن</t>
+          <t>درک شفاهی | بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | تشخیص گفتار | وضوح گفتار | بینایی دور | بینایی نزدیک | توجه انتخابی | زمان عکس‌العمل | ترتیب‌دهی اطلاعات | استدلال استقرایی | توجه شنیداری | هماهنگی چند عضو | جهت‌گیری فضایی | استقامت | قدرت ایستا | هماهنگی کلی بدن | درک عمق | تقسیم توجه | قدرت تنه | قدرت پویا | حفظ کردن | بینایی در شب | تعادل کلی بدن</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>افسران گشت پلیس و کلانتری | سرپرستان رده‌اول پلیس و کارآگاهان | کارآگاهان و بازرسان جنایی | آتش‌نشانان | سرپرستان رده‌اول آتش‌نشانی و پیشگیری از حریق | نگهبانان و ماموران حفاظتی | افسران و زندانبانان ندامتگاه‌ها | مدیران مدیریت بحران و فوریت‌ها | ماموران بازرسی امنیت حمل‌ونقل | تکنسین‌های فوریت‌های پزشکی | مدیران ارشد و عملیاتی | کارشناسان لجستیک و زنجیره تامین | مدیران حمل‌ونقل، انبارداری و توزیع | مدیران عامل و مدیران ارشد اجرایی | کارشناسان آموزش و توسعه منابع انسانی | کارشناسان بهداشت حرفه‌ای و ایمنی کار | کارشناسان نظارت و انطباق با مقررات | تکنسین‌های نقشه‌برداری | تکنسین‌های مواد ناریه، مهمات و انفجار | کارگران پاکسازی و دفع مواد خطرناک</t>
+          <t>ماموران گشت پلیس و کلانتری | سرپرستان رده‌اول پلیس و کارآگاهان | کارآگاهان و بازرسان جنایی | آتش‌نشانان | سرپرستان رده‌اول آتش‌نشانی و خدمات ایمنی و پیشگیری | نگهبانان و ماموران حراست | مأموران زندان و بازداشتگاه | مدیران مدیریت بحران و پدافند غیرعامل | ماموران بازرسی و کنترل امنیتی حمل‌ونقل | تکنسین‌های فوریت‌های پزشکی | مدیران کل و مدیران عملیات | کارشناسان لجستیک و مدیریت زنجیره تأمین | مدیران حمل‌ونقل، انبارداری و توزیع | مدیران عامل و مدیران ارشد اجرایی | کارشناسان آموزش و توسعه منابع انسانی | کارشناسان بهداشت حرفه‌ای و ایمنی کار | کارشناسان پایش انطباق و بازرسی مقرراتی | تکنسین‌های نقشه‌برداری و نقشه‌نگاری | کارشناسان مواد منفجره و آتش‌باری | کارگران امحا و پاک‌سازی مواد خطرناک</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -793,17 +793,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>نظارت | شنیدن فعال | تفکر انتقادی | سخن گفتن | درک مطلب | یادگیری فعال</t>
+          <t>نظارت | گوش دادن فعال | تفکر انتقادی | سخن گفتن | درک مطلب | یادگیری فعال</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ایمنی و امنیت عمومی | مکانیک | مخابرات | جغرافیا | زبان انگلیسی | رایانه و الکترونیک | حمل‌ونقل</t>
+          <t>ایمنی و امنیت عمومی | مکانیک | مخابرات | جغرافیا | زبان انگلیسی | رایانه و الکترونیک | حمل و نقل</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | تشخیص گفتار | وضوح گفتار | دید دور | دید نزدیک | توجه انتخابی | زمان واکنش | مرتب‌سازی اطلاعات | استدلال استقرایی | توجه شنیداری | هماهنگی چندعضوی | جهت‌یابی فضایی | استقامت | استحکام ایستا | هماهنگی کلی بدن | درک عمق | تقسیم توجه</t>
+          <t>درک شفاهی | بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | تشخیص گفتار | وضوح گفتار | بینایی دور | بینایی نزدیک | توجه انتخابی | زمان عکس‌العمل | ترتیب‌دهی اطلاعات | استدلال استقرایی | توجه شنیداری | هماهنگی چند عضو | جهت‌گیری فضایی | استقامت | قدرت ایستا | هماهنگی کلی بدن | درک عمق | تقسیم توجه</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>افسران گشت پلیس و کلانتری | سرپرستان رده‌اول پلیس و کارآگاهان | کارآگاهان و بازرسان جنایی | آتش‌نشانان | سرپرستان رده‌اول آتش‌نشانی و پیشگیری از حریق | نگهبانان و ماموران حفاظتی | افسران و زندانبانان ندامتگاه‌ها | مدیران مدیریت بحران و فوریت‌ها | ماموران بازرسی امنیت حمل‌ونقل | تکنسین‌های فوریت‌های پزشکی | مدیران ارشد و عملیاتی | کارشناسان لجستیک و زنجیره تامین | مدیران حمل‌ونقل، انبارداری و توزیع | مدیران عامل و مدیران ارشد اجرایی | کارشناسان آموزش و توسعه منابع انسانی | کارشناسان بهداشت حرفه‌ای و ایمنی کار | کارشناسان نظارت و انطباق با مقررات | تکنسین‌های نقشه‌برداری | تکنسین‌های مواد ناریه، مهمات و انفجار | کارگران پاکسازی و دفع مواد خطرناک</t>
+          <t>ماموران گشت پلیس و کلانتری | سرپرستان رده‌اول پلیس و کارآگاهان | کارآگاهان و بازرسان جنایی | آتش‌نشانان | سرپرستان رده‌اول آتش‌نشانی و خدمات ایمنی و پیشگیری | نگهبانان و ماموران حراست | مأموران زندان و بازداشتگاه | مدیران مدیریت بحران و پدافند غیرعامل | ماموران بازرسی و کنترل امنیتی حمل‌ونقل | تکنسین‌های فوریت‌های پزشکی | مدیران کل و مدیران عملیات | کارشناسان لجستیک و مدیریت زنجیره تأمین | مدیران حمل‌ونقل، انبارداری و توزیع | مدیران عامل و مدیران ارشد اجرایی | کارشناسان آموزش و توسعه منابع انسانی | کارشناسان بهداشت حرفه‌ای و ایمنی کار | کارشناسان پایش انطباق و بازرسی مقرراتی | تکنسین‌های نقشه‌برداری و نقشه‌نگاری | کارشناسان مواد منفجره و آتش‌باری | کارگران امحا و پاک‌سازی مواد خطرناک</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
